--- a/app/static/storage/July 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/July 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79BAAAA7-EC2D-482D-9BF7-CEA17109507E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5ABD1-93BC-48C4-B883-734B4810A161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -3234,11 +3234,65 @@
     <xf numFmtId="3" fontId="29" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3352,6 +3406,11 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3369,69 +3428,10 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3934,23 +3934,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="270" t="s">
+      <c r="A3" s="285" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="271"/>
-      <c r="C3" s="271"/>
-      <c r="D3" s="271"/>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="271"/>
-      <c r="I3" s="271"/>
-      <c r="J3" s="271"/>
-      <c r="K3" s="271"/>
-      <c r="L3" s="271"/>
-      <c r="M3" s="271"/>
-      <c r="N3" s="271"/>
-      <c r="O3" s="271"/>
+      <c r="B3" s="286"/>
+      <c r="C3" s="286"/>
+      <c r="D3" s="286"/>
+      <c r="E3" s="286"/>
+      <c r="F3" s="286"/>
+      <c r="G3" s="286"/>
+      <c r="H3" s="286"/>
+      <c r="I3" s="286"/>
+      <c r="J3" s="286"/>
+      <c r="K3" s="286"/>
+      <c r="L3" s="286"/>
+      <c r="M3" s="286"/>
+      <c r="N3" s="286"/>
+      <c r="O3" s="286"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -3958,23 +3958,23 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="272" t="s">
+      <c r="A4" s="287" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="271"/>
-      <c r="C4" s="271"/>
-      <c r="D4" s="271"/>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="271"/>
-      <c r="J4" s="271"/>
-      <c r="K4" s="271"/>
-      <c r="L4" s="271"/>
-      <c r="M4" s="271"/>
-      <c r="N4" s="271"/>
-      <c r="O4" s="271"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
+      <c r="K4" s="286"/>
+      <c r="L4" s="286"/>
+      <c r="M4" s="286"/>
+      <c r="N4" s="286"/>
+      <c r="O4" s="286"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -3999,62 +3999,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="261" t="s">
+      <c r="A6" s="276" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="262"/>
-      <c r="C6" s="262"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="273" t="s">
+      <c r="B6" s="277"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="288" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="274"/>
-      <c r="I6" s="274"/>
-      <c r="J6" s="274"/>
-      <c r="K6" s="274"/>
-      <c r="L6" s="274"/>
-      <c r="M6" s="274"/>
-      <c r="N6" s="274"/>
-      <c r="O6" s="238"/>
+      <c r="F6" s="289"/>
+      <c r="G6" s="289"/>
+      <c r="H6" s="289"/>
+      <c r="I6" s="289"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="289"/>
+      <c r="L6" s="289"/>
+      <c r="M6" s="289"/>
+      <c r="N6" s="289"/>
+      <c r="O6" s="253"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="264"/>
-      <c r="B7" s="265"/>
-      <c r="C7" s="265"/>
-      <c r="D7" s="266"/>
-      <c r="E7" s="255" t="s">
+      <c r="A7" s="279"/>
+      <c r="B7" s="280"/>
+      <c r="C7" s="280"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="270" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="239" t="s">
+      <c r="F7" s="254" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="239" t="s">
+      <c r="G7" s="254" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="242" t="s">
+      <c r="H7" s="257" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="242" t="s">
+      <c r="I7" s="257" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="242" t="s">
+      <c r="J7" s="257" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="239" t="s">
+      <c r="K7" s="254" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="239" t="s">
+      <c r="L7" s="254" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="242" t="s">
+      <c r="M7" s="257" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="258" t="s">
+      <c r="N7" s="273" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="275" t="s">
+      <c r="O7" s="290" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4065,17 +4065,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="256"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
-      <c r="M8" s="240"/>
-      <c r="N8" s="259"/>
-      <c r="O8" s="269"/>
+      <c r="E8" s="271"/>
+      <c r="F8" s="255"/>
+      <c r="G8" s="255"/>
+      <c r="H8" s="255"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="255"/>
+      <c r="K8" s="255"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="255"/>
+      <c r="N8" s="274"/>
+      <c r="O8" s="284"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4086,86 +4086,86 @@
       <c r="D9" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="256"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="240"/>
-      <c r="K9" s="240"/>
-      <c r="L9" s="240"/>
-      <c r="M9" s="240"/>
-      <c r="N9" s="259"/>
-      <c r="O9" s="269"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="255"/>
+      <c r="K9" s="255"/>
+      <c r="L9" s="255"/>
+      <c r="M9" s="255"/>
+      <c r="N9" s="274"/>
+      <c r="O9" s="284"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="260" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="246"/>
-      <c r="C10" s="247"/>
+      <c r="B10" s="261"/>
+      <c r="C10" s="262"/>
       <c r="D10" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="256"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="240"/>
-      <c r="K10" s="240"/>
-      <c r="L10" s="240"/>
-      <c r="M10" s="240"/>
-      <c r="N10" s="259"/>
-      <c r="O10" s="269"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="255"/>
+      <c r="K10" s="255"/>
+      <c r="L10" s="255"/>
+      <c r="M10" s="255"/>
+      <c r="N10" s="274"/>
+      <c r="O10" s="284"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="260" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="246"/>
-      <c r="C11" s="247"/>
+      <c r="B11" s="261"/>
+      <c r="C11" s="262"/>
       <c r="D11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="256"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="240"/>
-      <c r="K11" s="240"/>
-      <c r="L11" s="240"/>
-      <c r="M11" s="240"/>
-      <c r="N11" s="259"/>
-      <c r="O11" s="269"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
+      <c r="M11" s="255"/>
+      <c r="N11" s="274"/>
+      <c r="O11" s="284"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="245" t="s">
+      <c r="A12" s="260" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="246"/>
-      <c r="C12" s="247"/>
+      <c r="B12" s="261"/>
+      <c r="C12" s="262"/>
       <c r="D12" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="257"/>
-      <c r="F12" s="241"/>
-      <c r="G12" s="241"/>
-      <c r="H12" s="241"/>
-      <c r="I12" s="241"/>
-      <c r="J12" s="241"/>
-      <c r="K12" s="241"/>
-      <c r="L12" s="241"/>
-      <c r="M12" s="241"/>
-      <c r="N12" s="260"/>
-      <c r="O12" s="266"/>
+      <c r="E12" s="272"/>
+      <c r="F12" s="256"/>
+      <c r="G12" s="256"/>
+      <c r="H12" s="256"/>
+      <c r="I12" s="256"/>
+      <c r="J12" s="256"/>
+      <c r="K12" s="256"/>
+      <c r="L12" s="256"/>
+      <c r="M12" s="256"/>
+      <c r="N12" s="275"/>
+      <c r="O12" s="281"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="267"/>
-      <c r="B13" s="268"/>
-      <c r="C13" s="268"/>
-      <c r="D13" s="269"/>
+      <c r="A13" s="282"/>
+      <c r="B13" s="283"/>
+      <c r="C13" s="283"/>
+      <c r="D13" s="284"/>
       <c r="E13" s="20" t="s">
         <v>70</v>
       </c>
@@ -4207,10 +4207,10 @@
       <c r="B14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="276" t="s">
+      <c r="C14" s="291" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="238"/>
+      <c r="D14" s="253"/>
       <c r="E14" s="210">
         <v>0</v>
       </c>
@@ -4253,10 +4253,10 @@
       <c r="B15" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="254" t="s">
+      <c r="C15" s="269" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="238"/>
+      <c r="D15" s="253"/>
       <c r="E15" s="210">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
@@ -4303,16 +4303,16 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="249" t="s">
+      <c r="A16" s="264" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="277" t="s">
+      <c r="C16" s="292" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="278"/>
+      <c r="D16" s="293"/>
       <c r="E16" s="211">
         <v>0</v>
       </c>
@@ -4349,14 +4349,14 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="250"/>
+      <c r="A17" s="265"/>
       <c r="B17" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="243" t="s">
+      <c r="C17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="244"/>
+      <c r="D17" s="259"/>
       <c r="E17" s="211">
         <v>0</v>
       </c>
@@ -4393,14 +4393,14 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="251"/>
+      <c r="A18" s="266"/>
       <c r="B18" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="267" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="253"/>
+      <c r="D18" s="268"/>
       <c r="E18" s="211">
         <v>0</v>
       </c>
@@ -4443,10 +4443,10 @@
       <c r="B19" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="254" t="s">
+      <c r="C19" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="238"/>
+      <c r="D19" s="253"/>
       <c r="E19" s="210">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
@@ -4493,16 +4493,16 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="249" t="s">
+      <c r="A20" s="264" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="277" t="s">
+      <c r="C20" s="292" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="278"/>
+      <c r="D20" s="293"/>
       <c r="E20" s="212">
         <v>0</v>
       </c>
@@ -4539,14 +4539,14 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="250"/>
+      <c r="A21" s="265"/>
       <c r="B21" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="248" t="s">
+      <c r="C21" s="263" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="244"/>
+      <c r="D21" s="259"/>
       <c r="E21" s="211">
         <v>0</v>
       </c>
@@ -4583,14 +4583,14 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="250"/>
+      <c r="A22" s="265"/>
       <c r="B22" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="243" t="s">
+      <c r="C22" s="258" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="244"/>
+      <c r="D22" s="259"/>
       <c r="E22" s="211">
         <v>0</v>
       </c>
@@ -4627,14 +4627,14 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="251"/>
+      <c r="A23" s="266"/>
       <c r="B23" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="252" t="s">
+      <c r="C23" s="267" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="253"/>
+      <c r="D23" s="268"/>
       <c r="E23" s="213">
         <v>0</v>
       </c>
@@ -4677,10 +4677,10 @@
       <c r="B24" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="237" t="s">
+      <c r="C24" s="252" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="238"/>
+      <c r="D24" s="253"/>
       <c r="E24" s="29">
         <f t="shared" ref="E24:N24" si="3">(E14+E15)-E19</f>
         <v>0</v>
@@ -4733,23 +4733,43 @@
       <c r="B25" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="237" t="s">
+      <c r="C25" s="252" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="214"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
-      <c r="L25" s="41"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
+      <c r="D25" s="253"/>
+      <c r="E25" s="41">
+        <v>0</v>
+      </c>
+      <c r="F25" s="214">
+        <v>0</v>
+      </c>
+      <c r="G25" s="41">
+        <v>0</v>
+      </c>
+      <c r="H25" s="41">
+        <v>0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>2</v>
+      </c>
+      <c r="J25" s="41">
+        <v>1</v>
+      </c>
+      <c r="K25" s="41">
+        <v>0</v>
+      </c>
+      <c r="L25" s="41">
+        <v>0</v>
+      </c>
+      <c r="M25" s="42">
+        <v>0</v>
+      </c>
+      <c r="N25" s="42">
+        <v>4</v>
+      </c>
       <c r="O25" s="228">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:15" s="46" customFormat="1" x14ac:dyDescent="0.2">
@@ -4934,7 +4954,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="14" scale="91" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="133" scale="91" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4986,98 +5006,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="284" t="s">
+      <c r="A3" s="299" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="285"/>
-      <c r="C3" s="285"/>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="285"/>
-      <c r="K3" s="285"/>
-      <c r="L3" s="286"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="300"/>
+      <c r="D3" s="300"/>
+      <c r="E3" s="300"/>
+      <c r="F3" s="300"/>
+      <c r="G3" s="300"/>
+      <c r="H3" s="300"/>
+      <c r="I3" s="300"/>
+      <c r="J3" s="300"/>
+      <c r="K3" s="300"/>
+      <c r="L3" s="301"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="291" t="s">
+      <c r="A4" s="306" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="292"/>
-      <c r="C4" s="292"/>
-      <c r="D4" s="292"/>
-      <c r="E4" s="292"/>
-      <c r="F4" s="292"/>
-      <c r="G4" s="292"/>
-      <c r="H4" s="292"/>
-      <c r="I4" s="292"/>
-      <c r="J4" s="292"/>
-      <c r="K4" s="292"/>
-      <c r="L4" s="293"/>
+      <c r="B4" s="307"/>
+      <c r="C4" s="307"/>
+      <c r="D4" s="307"/>
+      <c r="E4" s="307"/>
+      <c r="F4" s="307"/>
+      <c r="G4" s="307"/>
+      <c r="H4" s="307"/>
+      <c r="I4" s="307"/>
+      <c r="J4" s="307"/>
+      <c r="K4" s="307"/>
+      <c r="L4" s="308"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="287"/>
-      <c r="F5" s="288"/>
-      <c r="G5" s="288"/>
-      <c r="H5" s="288"/>
-      <c r="I5" s="288"/>
-      <c r="J5" s="288"/>
-      <c r="K5" s="288"/>
-      <c r="L5" s="289"/>
+      <c r="E5" s="302"/>
+      <c r="F5" s="303"/>
+      <c r="G5" s="303"/>
+      <c r="H5" s="303"/>
+      <c r="I5" s="303"/>
+      <c r="J5" s="303"/>
+      <c r="K5" s="303"/>
+      <c r="L5" s="304"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="261" t="s">
+      <c r="A6" s="276" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="262"/>
-      <c r="C6" s="262"/>
-      <c r="D6" s="263"/>
-      <c r="E6" s="295" t="s">
+      <c r="B6" s="277"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="310" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="274"/>
-      <c r="G6" s="274"/>
-      <c r="H6" s="274"/>
-      <c r="I6" s="274"/>
-      <c r="J6" s="274"/>
-      <c r="K6" s="238"/>
-      <c r="L6" s="279" t="s">
+      <c r="F6" s="289"/>
+      <c r="G6" s="289"/>
+      <c r="H6" s="289"/>
+      <c r="I6" s="289"/>
+      <c r="J6" s="289"/>
+      <c r="K6" s="253"/>
+      <c r="L6" s="294" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="264"/>
-      <c r="B7" s="265"/>
-      <c r="C7" s="265"/>
-      <c r="D7" s="266"/>
-      <c r="E7" s="255" t="s">
+      <c r="A7" s="279"/>
+      <c r="B7" s="280"/>
+      <c r="C7" s="280"/>
+      <c r="D7" s="281"/>
+      <c r="E7" s="270" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="242" t="s">
+      <c r="F7" s="257" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="239" t="s">
+      <c r="G7" s="254" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="239" t="s">
+      <c r="H7" s="254" t="s">
         <v>121</v>
       </c>
-      <c r="I7" s="239" t="s">
+      <c r="I7" s="254" t="s">
         <v>122</v>
       </c>
-      <c r="J7" s="281" t="s">
+      <c r="J7" s="296" t="s">
         <v>123</v>
       </c>
-      <c r="K7" s="294" t="s">
+      <c r="K7" s="309" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="280"/>
+      <c r="L7" s="295"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5089,14 +5109,14 @@
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="256"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="282"/>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
+      <c r="E8" s="271"/>
+      <c r="F8" s="255"/>
+      <c r="G8" s="255"/>
+      <c r="H8" s="255"/>
+      <c r="I8" s="255"/>
+      <c r="J8" s="297"/>
+      <c r="K8" s="295"/>
+      <c r="L8" s="295"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5108,77 +5128,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="256"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="240"/>
-      <c r="J9" s="282"/>
-      <c r="K9" s="280"/>
-      <c r="L9" s="280"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="255"/>
+      <c r="G9" s="255"/>
+      <c r="H9" s="255"/>
+      <c r="I9" s="255"/>
+      <c r="J9" s="297"/>
+      <c r="K9" s="295"/>
+      <c r="L9" s="295"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="260" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="246"/>
-      <c r="C10" s="247"/>
+      <c r="B10" s="261"/>
+      <c r="C10" s="262"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="256"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="240"/>
-      <c r="J10" s="282"/>
-      <c r="K10" s="280"/>
-      <c r="L10" s="280"/>
+      <c r="E10" s="271"/>
+      <c r="F10" s="255"/>
+      <c r="G10" s="255"/>
+      <c r="H10" s="255"/>
+      <c r="I10" s="255"/>
+      <c r="J10" s="297"/>
+      <c r="K10" s="295"/>
+      <c r="L10" s="295"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="245" t="s">
+      <c r="A11" s="260" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="246"/>
-      <c r="C11" s="247"/>
+      <c r="B11" s="261"/>
+      <c r="C11" s="262"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="256"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="240"/>
-      <c r="J11" s="282"/>
-      <c r="K11" s="280"/>
-      <c r="L11" s="280"/>
+      <c r="E11" s="271"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="297"/>
+      <c r="K11" s="295"/>
+      <c r="L11" s="295"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="245" t="s">
+      <c r="A12" s="260" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="246"/>
-      <c r="C12" s="247"/>
+      <c r="B12" s="261"/>
+      <c r="C12" s="262"/>
       <c r="D12" s="229" t="str">
         <f>'Page 1'!D12</f>
         <v>July 2026</v>
       </c>
-      <c r="E12" s="257"/>
-      <c r="F12" s="241"/>
-      <c r="G12" s="241"/>
-      <c r="H12" s="241"/>
-      <c r="I12" s="241"/>
-      <c r="J12" s="283"/>
-      <c r="K12" s="280"/>
-      <c r="L12" s="280"/>
+      <c r="E12" s="272"/>
+      <c r="F12" s="256"/>
+      <c r="G12" s="256"/>
+      <c r="H12" s="256"/>
+      <c r="I12" s="256"/>
+      <c r="J12" s="298"/>
+      <c r="K12" s="295"/>
+      <c r="L12" s="295"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="267"/>
-      <c r="B13" s="290"/>
-      <c r="C13" s="290"/>
-      <c r="D13" s="269"/>
+      <c r="A13" s="282"/>
+      <c r="B13" s="305"/>
+      <c r="C13" s="305"/>
+      <c r="D13" s="284"/>
       <c r="E13" s="73" t="s">
         <v>125</v>
       </c>
@@ -5211,10 +5231,10 @@
       <c r="B14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="276" t="s">
+      <c r="C14" s="291" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="238"/>
+      <c r="D14" s="253"/>
       <c r="E14" s="28">
         <v>4</v>
       </c>
@@ -5249,10 +5269,10 @@
       <c r="B15" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="254" t="s">
+      <c r="C15" s="269" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="238"/>
+      <c r="D15" s="253"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>2</v>
@@ -5287,16 +5307,16 @@
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="249" t="s">
+      <c r="A16" s="264" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="277" t="s">
+      <c r="C16" s="292" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="278"/>
+      <c r="D16" s="293"/>
       <c r="E16" s="78">
         <v>2</v>
       </c>
@@ -5325,14 +5345,14 @@
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="250"/>
+      <c r="A17" s="265"/>
       <c r="B17" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="243" t="s">
+      <c r="C17" s="258" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="244"/>
+      <c r="D17" s="259"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5361,14 +5381,14 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="251"/>
+      <c r="A18" s="266"/>
       <c r="B18" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="252" t="s">
+      <c r="C18" s="267" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="253"/>
+      <c r="D18" s="268"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5403,10 +5423,10 @@
       <c r="B19" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="254" t="s">
+      <c r="C19" s="269" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="238"/>
+      <c r="D19" s="253"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
         <v>5</v>
@@ -5441,16 +5461,16 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="249" t="s">
+      <c r="A20" s="264" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="277" t="s">
+      <c r="C20" s="292" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="278"/>
+      <c r="D20" s="293"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5479,14 +5499,14 @@
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="250"/>
+      <c r="A21" s="265"/>
       <c r="B21" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="248" t="s">
+      <c r="C21" s="263" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="244"/>
+      <c r="D21" s="259"/>
       <c r="E21" s="33">
         <v>5</v>
       </c>
@@ -5515,14 +5535,14 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="250"/>
+      <c r="A22" s="265"/>
       <c r="B22" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="243" t="s">
+      <c r="C22" s="258" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="244"/>
+      <c r="D22" s="259"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5551,14 +5571,14 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="251"/>
+      <c r="A23" s="266"/>
       <c r="B23" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="252" t="s">
+      <c r="C23" s="267" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="253"/>
+      <c r="D23" s="268"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5596,10 +5616,10 @@
       <c r="B24" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="237" t="s">
+      <c r="C24" s="252" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="238"/>
+      <c r="D24" s="253"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
         <v>1</v>
@@ -5640,17 +5660,31 @@
       <c r="B25" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="237" t="s">
+      <c r="C25" s="252" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="238"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="77"/>
+      <c r="D25" s="253"/>
+      <c r="E25" s="40">
+        <v>0</v>
+      </c>
+      <c r="F25" s="90">
+        <v>0</v>
+      </c>
+      <c r="G25" s="41">
+        <v>0</v>
+      </c>
+      <c r="H25" s="41">
+        <v>0</v>
+      </c>
+      <c r="I25" s="41">
+        <v>0</v>
+      </c>
+      <c r="J25" s="42">
+        <v>0</v>
+      </c>
+      <c r="K25" s="77">
+        <v>0</v>
+      </c>
       <c r="L25" s="91"/>
     </row>
     <row r="26" spans="1:27" s="53" customFormat="1" x14ac:dyDescent="0.15">
@@ -5842,7 +5876,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="14" scale="95" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="256" scale="95" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5875,85 +5909,85 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="303" t="s">
+      <c r="A3" s="311" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="304"/>
-      <c r="C3" s="305"/>
-      <c r="D3" s="305"/>
-      <c r="E3" s="305"/>
-      <c r="F3" s="304"/>
-      <c r="G3" s="304"/>
+      <c r="B3" s="312"/>
+      <c r="C3" s="313"/>
+      <c r="D3" s="313"/>
+      <c r="E3" s="313"/>
+      <c r="F3" s="312"/>
+      <c r="G3" s="312"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="306"/>
-      <c r="B4" s="304"/>
-      <c r="C4" s="305"/>
-      <c r="D4" s="305"/>
-      <c r="E4" s="305"/>
-      <c r="F4" s="304"/>
-      <c r="G4" s="304"/>
+      <c r="A4" s="238"/>
+      <c r="B4" s="312"/>
+      <c r="C4" s="313"/>
+      <c r="D4" s="313"/>
+      <c r="E4" s="313"/>
+      <c r="F4" s="312"/>
+      <c r="G4" s="312"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="299" t="s">
+      <c r="A5" s="317" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="301" t="s">
+      <c r="B5" s="319" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="302" t="s">
+      <c r="C5" s="320" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="300" t="s">
+      <c r="D5" s="318" t="s">
         <v>143</v>
       </c>
-      <c r="E5" s="300" t="s">
+      <c r="E5" s="318" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="301" t="s">
+      <c r="F5" s="319" t="s">
         <v>145</v>
       </c>
-      <c r="G5" s="301" t="s">
+      <c r="G5" s="319" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="240"/>
-      <c r="B6" s="240"/>
-      <c r="C6" s="240"/>
-      <c r="D6" s="240"/>
-      <c r="E6" s="240"/>
-      <c r="F6" s="240"/>
-      <c r="G6" s="240"/>
+      <c r="A6" s="255"/>
+      <c r="B6" s="255"/>
+      <c r="C6" s="255"/>
+      <c r="D6" s="255"/>
+      <c r="E6" s="255"/>
+      <c r="F6" s="255"/>
+      <c r="G6" s="255"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="240"/>
-      <c r="B7" s="240"/>
-      <c r="C7" s="240"/>
-      <c r="D7" s="240"/>
-      <c r="E7" s="240"/>
-      <c r="F7" s="240"/>
-      <c r="G7" s="240"/>
+      <c r="A7" s="255"/>
+      <c r="B7" s="255"/>
+      <c r="C7" s="255"/>
+      <c r="D7" s="255"/>
+      <c r="E7" s="255"/>
+      <c r="F7" s="255"/>
+      <c r="G7" s="255"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="241"/>
-      <c r="B8" s="241"/>
-      <c r="C8" s="241"/>
-      <c r="D8" s="241"/>
-      <c r="E8" s="241"/>
-      <c r="F8" s="241"/>
-      <c r="G8" s="241"/>
+      <c r="A8" s="256"/>
+      <c r="B8" s="256"/>
+      <c r="C8" s="256"/>
+      <c r="D8" s="256"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="256"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="296" t="s">
+      <c r="A9" s="314" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="297"/>
-      <c r="C9" s="297"/>
-      <c r="D9" s="297"/>
-      <c r="E9" s="297"/>
-      <c r="F9" s="297"/>
-      <c r="G9" s="298"/>
+      <c r="B9" s="315"/>
+      <c r="C9" s="315"/>
+      <c r="D9" s="315"/>
+      <c r="E9" s="315"/>
+      <c r="F9" s="315"/>
+      <c r="G9" s="316"/>
     </row>
     <row r="10" spans="1:7" s="129" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="132"/>
@@ -6046,15 +6080,15 @@
       <c r="G19" s="135"/>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="296" t="s">
+      <c r="A20" s="314" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="297"/>
-      <c r="C20" s="297"/>
-      <c r="D20" s="297"/>
-      <c r="E20" s="297"/>
-      <c r="F20" s="297"/>
-      <c r="G20" s="298"/>
+      <c r="B20" s="315"/>
+      <c r="C20" s="315"/>
+      <c r="D20" s="315"/>
+      <c r="E20" s="315"/>
+      <c r="F20" s="315"/>
+      <c r="G20" s="316"/>
     </row>
     <row r="21" spans="1:7" s="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="132"/>
@@ -6173,7 +6207,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="14" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="256" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="1048575" man="1"/>
   </colBreaks>
@@ -6206,11 +6240,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="321" t="s">
         <v>150</v>
       </c>
       <c r="B1" s="235"/>
-      <c r="C1" s="236"/>
+      <c r="C1" s="322"/>
       <c r="F1" s="148" t="s">
         <v>151</v>
       </c>
@@ -6226,7 +6260,7 @@
       </c>
       <c r="C2" s="150">
         <f>SUM(D3:D6)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" s="151"/>
       <c r="G2" s="120" t="s">
@@ -6258,7 +6292,7 @@
       </c>
       <c r="C4" s="151"/>
       <c r="D4" s="155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" s="120" t="s">
         <v>158</v>
@@ -6274,7 +6308,7 @@
       </c>
       <c r="C5" s="151"/>
       <c r="D5" s="155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="120" t="s">
         <v>160</v>
@@ -6290,7 +6324,7 @@
       </c>
       <c r="C6" s="157"/>
       <c r="D6" s="158">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6300,7 +6334,7 @@
       <c r="C7" s="151"/>
       <c r="D7" s="159">
         <f>SUM(C8:C13)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G7" s="120" t="s">
         <v>7</v>
@@ -6322,7 +6356,7 @@
       </c>
       <c r="I8" s="163"/>
       <c r="O8" s="164">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6354,7 +6388,7 @@
       </c>
       <c r="I10" s="163"/>
       <c r="O10" s="165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="166"/>
     </row>
@@ -6374,7 +6408,7 @@
         <v>171</v>
       </c>
       <c r="C12" s="155">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" s="151"/>
       <c r="I12" s="163"/>
@@ -6385,7 +6419,7 @@
         <v>172</v>
       </c>
       <c r="C13" s="155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="118"/>
       <c r="O13" s="167" t="s">
@@ -6478,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="151"/>
-      <c r="F20" s="234" t="s">
+      <c r="F20" s="321" t="s">
         <v>186</v>
       </c>
       <c r="G20" s="235"/>
@@ -6534,11 +6568,11 @@
         <v>196</v>
       </c>
       <c r="I22" s="171">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J22" s="124"/>
       <c r="K22" s="171">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L22" s="124"/>
       <c r="M22" s="171">
@@ -6555,7 +6589,7 @@
       <c r="R22" s="124"/>
       <c r="S22" s="172">
         <f t="shared" ref="S22:S32" si="0">SUM(I22+K22+M22+O22+Q22)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6575,7 +6609,7 @@
       </c>
       <c r="J23" s="124"/>
       <c r="K23" s="173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="124"/>
       <c r="M23" s="173">
@@ -6592,7 +6626,7 @@
       <c r="R23" s="124"/>
       <c r="S23" s="172">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -6946,12 +6980,12 @@
       </c>
       <c r="I33" s="172">
         <f>SUM(I22:I32)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J33" s="175"/>
       <c r="K33" s="172">
         <f>SUM(K22:K32)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L33" s="176"/>
       <c r="M33" s="172">
@@ -6970,7 +7004,7 @@
       </c>
       <c r="S33" s="172">
         <f>SUM(S22:S32)</f>
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7105,7 +7139,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="307" t="s">
+      <c r="A1" s="234" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="235"/>
@@ -7179,7 +7213,7 @@
         <v>5</v>
       </c>
       <c r="Z3" s="182">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7196,7 +7230,7 @@
       <c r="B5" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="313" t="s">
+      <c r="C5" s="242" t="s">
         <v>6</v>
       </c>
       <c r="D5" s="235"/>
@@ -7221,7 +7255,7 @@
       <c r="Z5" s="184"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="313" t="s">
+      <c r="C6" s="242" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="235"/>
@@ -7232,21 +7266,21 @@
         <v>0</v>
       </c>
       <c r="N6" s="181"/>
-      <c r="R6" s="322" t="s">
+      <c r="R6" s="251" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="317"/>
-      <c r="T6" s="317"/>
-      <c r="U6" s="317"/>
-      <c r="V6" s="317"/>
-      <c r="W6" s="317"/>
-      <c r="X6" s="317"/>
-      <c r="Y6" s="317"/>
-      <c r="Z6" s="317"/>
+      <c r="S6" s="246"/>
+      <c r="T6" s="246"/>
+      <c r="U6" s="246"/>
+      <c r="V6" s="246"/>
+      <c r="W6" s="246"/>
+      <c r="X6" s="246"/>
+      <c r="Y6" s="246"/>
+      <c r="Z6" s="246"/>
       <c r="AA6" s="185"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="313" t="s">
+      <c r="C7" s="242" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="235"/>
@@ -7257,15 +7291,15 @@
         <v>0</v>
       </c>
       <c r="N7" s="181"/>
-      <c r="R7" s="317"/>
-      <c r="S7" s="317"/>
-      <c r="T7" s="317"/>
-      <c r="U7" s="317"/>
-      <c r="V7" s="317"/>
-      <c r="W7" s="317"/>
-      <c r="X7" s="317"/>
-      <c r="Y7" s="317"/>
-      <c r="Z7" s="317"/>
+      <c r="R7" s="246"/>
+      <c r="S7" s="246"/>
+      <c r="T7" s="246"/>
+      <c r="U7" s="246"/>
+      <c r="V7" s="246"/>
+      <c r="W7" s="246"/>
+      <c r="X7" s="246"/>
+      <c r="Y7" s="246"/>
+      <c r="Z7" s="246"/>
       <c r="AA7" s="185"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7279,15 +7313,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="181"/>
-      <c r="R8" s="317"/>
-      <c r="S8" s="317"/>
-      <c r="T8" s="317"/>
-      <c r="U8" s="317"/>
-      <c r="V8" s="317"/>
-      <c r="W8" s="317"/>
-      <c r="X8" s="317"/>
-      <c r="Y8" s="317"/>
-      <c r="Z8" s="317"/>
+      <c r="R8" s="246"/>
+      <c r="S8" s="246"/>
+      <c r="T8" s="246"/>
+      <c r="U8" s="246"/>
+      <c r="V8" s="246"/>
+      <c r="W8" s="246"/>
+      <c r="X8" s="246"/>
+      <c r="Y8" s="246"/>
+      <c r="Z8" s="246"/>
       <c r="AA8" s="185"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7302,15 +7336,15 @@
         <v>14</v>
       </c>
       <c r="N9" s="181"/>
-      <c r="R9" s="311"/>
-      <c r="S9" s="311"/>
-      <c r="T9" s="311"/>
-      <c r="U9" s="311"/>
-      <c r="V9" s="311"/>
-      <c r="W9" s="311"/>
-      <c r="X9" s="311"/>
-      <c r="Y9" s="311"/>
-      <c r="Z9" s="311"/>
+      <c r="R9" s="240"/>
+      <c r="S9" s="240"/>
+      <c r="T9" s="240"/>
+      <c r="U9" s="240"/>
+      <c r="V9" s="240"/>
+      <c r="W9" s="240"/>
+      <c r="X9" s="240"/>
+      <c r="Y9" s="240"/>
+      <c r="Z9" s="240"/>
       <c r="AA9" s="149"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7388,7 +7422,7 @@
       <c r="N14" s="181"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="313" t="s">
+      <c r="C15" s="242" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="235"/>
@@ -7408,7 +7442,7 @@
       <c r="AA15" s="149"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="313" t="s">
+      <c r="C16" s="242" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="235"/>
@@ -7500,7 +7534,7 @@
       <c r="N21" s="181"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="318" t="s">
+      <c r="A23" s="247" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="235"/>
@@ -7534,88 +7568,88 @@
       <c r="A26" s="149"/>
       <c r="B26" s="194"/>
       <c r="C26" s="194"/>
-      <c r="D26" s="310" t="s">
+      <c r="D26" s="239" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="311"/>
-      <c r="F26" s="311"/>
-      <c r="G26" s="311"/>
-      <c r="H26" s="311"/>
-      <c r="I26" s="311"/>
-      <c r="J26" s="311"/>
-      <c r="K26" s="311"/>
-      <c r="L26" s="311"/>
+      <c r="E26" s="240"/>
+      <c r="F26" s="240"/>
+      <c r="G26" s="240"/>
+      <c r="H26" s="240"/>
+      <c r="I26" s="240"/>
+      <c r="J26" s="240"/>
+      <c r="K26" s="240"/>
+      <c r="L26" s="240"/>
       <c r="M26" s="194"/>
       <c r="N26" s="194"/>
       <c r="O26" s="149"/>
       <c r="P26" s="149"/>
       <c r="Q26" s="149"/>
-      <c r="R26" s="310" t="s">
+      <c r="R26" s="239" t="s">
         <v>30</v>
       </c>
-      <c r="S26" s="311"/>
-      <c r="T26" s="311"/>
-      <c r="U26" s="311"/>
-      <c r="V26" s="311"/>
-      <c r="W26" s="311"/>
-      <c r="X26" s="311"/>
-      <c r="Y26" s="311"/>
-      <c r="Z26" s="311"/>
+      <c r="S26" s="240"/>
+      <c r="T26" s="240"/>
+      <c r="U26" s="240"/>
+      <c r="V26" s="240"/>
+      <c r="W26" s="240"/>
+      <c r="X26" s="240"/>
+      <c r="Y26" s="240"/>
+      <c r="Z26" s="240"/>
       <c r="AA26" s="149"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C27" s="149"/>
-      <c r="D27" s="319" t="s">
+      <c r="D27" s="248" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="320"/>
-      <c r="F27" s="320"/>
-      <c r="G27" s="320"/>
-      <c r="H27" s="320"/>
-      <c r="I27" s="320"/>
-      <c r="J27" s="320"/>
-      <c r="K27" s="320"/>
-      <c r="L27" s="320"/>
+      <c r="E27" s="249"/>
+      <c r="F27" s="249"/>
+      <c r="G27" s="249"/>
+      <c r="H27" s="249"/>
+      <c r="I27" s="249"/>
+      <c r="J27" s="249"/>
+      <c r="K27" s="249"/>
+      <c r="L27" s="249"/>
       <c r="M27" s="149"/>
       <c r="N27" s="149"/>
       <c r="O27" s="149"/>
       <c r="P27" s="149"/>
       <c r="Q27" s="149"/>
-      <c r="R27" s="319" t="s">
+      <c r="R27" s="248" t="s">
         <v>32</v>
       </c>
-      <c r="S27" s="320"/>
-      <c r="T27" s="320"/>
-      <c r="U27" s="320"/>
-      <c r="V27" s="320"/>
-      <c r="W27" s="320"/>
-      <c r="X27" s="320"/>
-      <c r="Y27" s="320"/>
-      <c r="Z27" s="320"/>
+      <c r="S27" s="249"/>
+      <c r="T27" s="249"/>
+      <c r="U27" s="249"/>
+      <c r="V27" s="249"/>
+      <c r="W27" s="249"/>
+      <c r="X27" s="249"/>
+      <c r="Y27" s="249"/>
+      <c r="Z27" s="249"/>
       <c r="AA27" s="149"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="316"/>
-      <c r="E28" s="317"/>
-      <c r="F28" s="317"/>
-      <c r="G28" s="317"/>
-      <c r="H28" s="317"/>
-      <c r="I28" s="317"/>
-      <c r="J28" s="317"/>
-      <c r="K28" s="317"/>
-      <c r="L28" s="317"/>
-      <c r="R28" s="316"/>
-      <c r="S28" s="317"/>
-      <c r="T28" s="317"/>
-      <c r="U28" s="317"/>
-      <c r="V28" s="317"/>
-      <c r="W28" s="317"/>
-      <c r="X28" s="317"/>
-      <c r="Y28" s="317"/>
-      <c r="Z28" s="317"/>
+      <c r="D28" s="245"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="246"/>
+      <c r="G28" s="246"/>
+      <c r="H28" s="246"/>
+      <c r="I28" s="246"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="246"/>
+      <c r="L28" s="246"/>
+      <c r="R28" s="245"/>
+      <c r="S28" s="246"/>
+      <c r="T28" s="246"/>
+      <c r="U28" s="246"/>
+      <c r="V28" s="246"/>
+      <c r="W28" s="246"/>
+      <c r="X28" s="246"/>
+      <c r="Y28" s="246"/>
+      <c r="Z28" s="246"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="306" t="s">
+      <c r="D29" s="238" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="235"/>
@@ -7735,7 +7769,7 @@
       <c r="AA33" s="166"/>
     </row>
     <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="306" t="s">
+      <c r="A34" s="238" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="235"/>
@@ -7747,25 +7781,25 @@
       <c r="H34" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="312" t="str">
+      <c r="I34" s="241" t="str">
         <f ca="1">TEXT(TODAY(), "mmmm yyyy")</f>
         <v>August 2026</v>
       </c>
-      <c r="J34" s="311"/>
-      <c r="K34" s="311"/>
-      <c r="L34" s="311"/>
-      <c r="M34" s="311"/>
-      <c r="N34" s="311"/>
+      <c r="J34" s="240"/>
+      <c r="K34" s="240"/>
+      <c r="L34" s="240"/>
+      <c r="M34" s="240"/>
+      <c r="N34" s="240"/>
       <c r="O34" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="314" t="s">
+      <c r="P34" s="243" t="s">
         <v>40</v>
       </c>
-      <c r="Q34" s="315"/>
-      <c r="R34" s="315"/>
-      <c r="S34" s="315"/>
-      <c r="T34" s="315"/>
+      <c r="Q34" s="244"/>
+      <c r="R34" s="244"/>
+      <c r="S34" s="244"/>
+      <c r="T34" s="244"/>
       <c r="U34" s="184"/>
       <c r="V34" s="195"/>
       <c r="W34" s="195"/>
@@ -7783,16 +7817,16 @@
       <c r="AA36" s="198"/>
     </row>
     <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="321"/>
-      <c r="K37" s="311"/>
-      <c r="L37" s="311"/>
-      <c r="M37" s="311"/>
-      <c r="N37" s="311"/>
-      <c r="O37" s="311"/>
-      <c r="P37" s="311"/>
-      <c r="Q37" s="311"/>
-      <c r="R37" s="311"/>
-      <c r="S37" s="311"/>
+      <c r="J37" s="250"/>
+      <c r="K37" s="240"/>
+      <c r="L37" s="240"/>
+      <c r="M37" s="240"/>
+      <c r="N37" s="240"/>
+      <c r="O37" s="240"/>
+      <c r="P37" s="240"/>
+      <c r="Q37" s="240"/>
+      <c r="R37" s="240"/>
+      <c r="S37" s="240"/>
       <c r="T37" s="149"/>
       <c r="U37" s="149"/>
       <c r="V37" s="149"/>
@@ -7803,18 +7837,18 @@
       <c r="AA37" s="149"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="319" t="s">
+      <c r="J38" s="248" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="320"/>
-      <c r="L38" s="320"/>
-      <c r="M38" s="320"/>
-      <c r="N38" s="320"/>
-      <c r="O38" s="320"/>
-      <c r="P38" s="320"/>
-      <c r="Q38" s="320"/>
-      <c r="R38" s="320"/>
-      <c r="S38" s="320"/>
+      <c r="K38" s="249"/>
+      <c r="L38" s="249"/>
+      <c r="M38" s="249"/>
+      <c r="N38" s="249"/>
+      <c r="O38" s="249"/>
+      <c r="P38" s="249"/>
+      <c r="Q38" s="249"/>
+      <c r="R38" s="249"/>
+      <c r="S38" s="249"/>
       <c r="T38" s="149"/>
       <c r="U38" s="149"/>
       <c r="V38" s="149"/>
@@ -7825,12 +7859,12 @@
       <c r="AA38" s="149"/>
     </row>
     <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="309" t="s">
+      <c r="A40" s="237" t="s">
         <v>42</v>
       </c>
       <c r="B40" s="235"/>
       <c r="C40" s="235"/>
-      <c r="D40" s="308" t="s">
+      <c r="D40" s="236" t="s">
         <v>43</v>
       </c>
       <c r="E40" s="235"/>
@@ -7918,7 +7952,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="14" scale="90" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="256" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7947,7 +7981,7 @@
       <c r="H30" s="324"/>
       <c r="I30" s="324"/>
       <c r="J30" s="324"/>
-      <c r="K30" s="269"/>
+      <c r="K30" s="284"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D31" s="202"/>
@@ -7963,7 +7997,7 @@
       <c r="H32" s="324"/>
       <c r="I32" s="324"/>
       <c r="J32" s="324"/>
-      <c r="K32" s="269"/>
+      <c r="K32" s="284"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D33" s="202"/>
@@ -7979,7 +8013,7 @@
       <c r="H34" s="324"/>
       <c r="I34" s="324"/>
       <c r="J34" s="324"/>
-      <c r="K34" s="269"/>
+      <c r="K34" s="284"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D35" s="202"/>

--- a/app/static/storage/July 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
+++ b/app/static/storage/July 2026 MTC BUENAVISTA, AGUSAN DEL NORTE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5ABD1-93BC-48C4-B883-734B4810A161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E36F1E8-9B6B-43F2-B2E9-7F004EB389E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="363" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Page 1" sheetId="1" r:id="rId1"/>
@@ -3234,111 +3234,64 @@
     <xf numFmtId="3" fontId="29" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="109" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="115" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="116" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="114" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3368,22 +3321,26 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="77" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="112" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="110" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="111" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3403,35 +3360,78 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="87" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="89" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="108" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="108" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3934,23 +3934,23 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:20" s="8" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="285" t="s">
+      <c r="A3" s="271" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="286"/>
-      <c r="C3" s="286"/>
-      <c r="D3" s="286"/>
-      <c r="E3" s="286"/>
-      <c r="F3" s="286"/>
-      <c r="G3" s="286"/>
-      <c r="H3" s="286"/>
-      <c r="I3" s="286"/>
-      <c r="J3" s="286"/>
-      <c r="K3" s="286"/>
-      <c r="L3" s="286"/>
-      <c r="M3" s="286"/>
-      <c r="N3" s="286"/>
-      <c r="O3" s="286"/>
+      <c r="B3" s="272"/>
+      <c r="C3" s="272"/>
+      <c r="D3" s="272"/>
+      <c r="E3" s="272"/>
+      <c r="F3" s="272"/>
+      <c r="G3" s="272"/>
+      <c r="H3" s="272"/>
+      <c r="I3" s="272"/>
+      <c r="J3" s="272"/>
+      <c r="K3" s="272"/>
+      <c r="L3" s="272"/>
+      <c r="M3" s="272"/>
+      <c r="N3" s="272"/>
+      <c r="O3" s="272"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
@@ -3958,23 +3958,23 @@
       <c r="T3" s="7"/>
     </row>
     <row r="4" spans="1:20" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="287" t="s">
+      <c r="A4" s="273" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="286"/>
-      <c r="C4" s="286"/>
-      <c r="D4" s="286"/>
-      <c r="E4" s="286"/>
-      <c r="F4" s="286"/>
-      <c r="G4" s="286"/>
-      <c r="H4" s="286"/>
-      <c r="I4" s="286"/>
-      <c r="J4" s="286"/>
-      <c r="K4" s="286"/>
-      <c r="L4" s="286"/>
-      <c r="M4" s="286"/>
-      <c r="N4" s="286"/>
-      <c r="O4" s="286"/>
+      <c r="B4" s="272"/>
+      <c r="C4" s="272"/>
+      <c r="D4" s="272"/>
+      <c r="E4" s="272"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="272"/>
+      <c r="H4" s="272"/>
+      <c r="I4" s="272"/>
+      <c r="J4" s="272"/>
+      <c r="K4" s="272"/>
+      <c r="L4" s="272"/>
+      <c r="M4" s="272"/>
+      <c r="N4" s="272"/>
+      <c r="O4" s="272"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
@@ -3999,62 +3999,62 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="276" t="s">
+      <c r="A6" s="262" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="288" t="s">
+      <c r="B6" s="263"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="274" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="289"/>
-      <c r="I6" s="289"/>
-      <c r="J6" s="289"/>
-      <c r="K6" s="289"/>
-      <c r="L6" s="289"/>
-      <c r="M6" s="289"/>
-      <c r="N6" s="289"/>
-      <c r="O6" s="253"/>
+      <c r="F6" s="275"/>
+      <c r="G6" s="275"/>
+      <c r="H6" s="275"/>
+      <c r="I6" s="275"/>
+      <c r="J6" s="275"/>
+      <c r="K6" s="275"/>
+      <c r="L6" s="275"/>
+      <c r="M6" s="275"/>
+      <c r="N6" s="275"/>
+      <c r="O6" s="248"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="279"/>
-      <c r="B7" s="280"/>
-      <c r="C7" s="280"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="270" t="s">
+      <c r="A7" s="265"/>
+      <c r="B7" s="266"/>
+      <c r="C7" s="266"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="284" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="254" t="s">
+      <c r="F7" s="251" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="254" t="s">
+      <c r="G7" s="251" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="257" t="s">
+      <c r="H7" s="277" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="257" t="s">
+      <c r="I7" s="277" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="257" t="s">
+      <c r="J7" s="277" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="254" t="s">
+      <c r="K7" s="251" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="254" t="s">
+      <c r="L7" s="251" t="s">
         <v>57</v>
       </c>
-      <c r="M7" s="257" t="s">
+      <c r="M7" s="277" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="273" t="s">
+      <c r="N7" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="O7" s="290" t="s">
+      <c r="O7" s="276" t="s">
         <v>60</v>
       </c>
     </row>
@@ -4065,17 +4065,17 @@
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="271"/>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="255"/>
-      <c r="J8" s="255"/>
-      <c r="K8" s="255"/>
-      <c r="L8" s="255"/>
-      <c r="M8" s="255"/>
-      <c r="N8" s="274"/>
-      <c r="O8" s="284"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="242"/>
+      <c r="K8" s="242"/>
+      <c r="L8" s="242"/>
+      <c r="M8" s="242"/>
+      <c r="N8" s="257"/>
+      <c r="O8" s="270"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -4086,86 +4086,86 @@
       <c r="D9" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="271"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="255"/>
-      <c r="K9" s="255"/>
-      <c r="L9" s="255"/>
-      <c r="M9" s="255"/>
-      <c r="N9" s="274"/>
-      <c r="O9" s="284"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="242"/>
+      <c r="K9" s="242"/>
+      <c r="L9" s="242"/>
+      <c r="M9" s="242"/>
+      <c r="N9" s="257"/>
+      <c r="O9" s="270"/>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="260" t="s">
+      <c r="A10" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="261"/>
-      <c r="C10" s="262"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="261"/>
       <c r="D10" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="271"/>
-      <c r="F10" s="255"/>
-      <c r="G10" s="255"/>
-      <c r="H10" s="255"/>
-      <c r="I10" s="255"/>
-      <c r="J10" s="255"/>
-      <c r="K10" s="255"/>
-      <c r="L10" s="255"/>
-      <c r="M10" s="255"/>
-      <c r="N10" s="274"/>
-      <c r="O10" s="284"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="242"/>
+      <c r="K10" s="242"/>
+      <c r="L10" s="242"/>
+      <c r="M10" s="242"/>
+      <c r="N10" s="257"/>
+      <c r="O10" s="270"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="260" t="s">
+      <c r="A11" s="259" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="261"/>
-      <c r="C11" s="262"/>
+      <c r="B11" s="260"/>
+      <c r="C11" s="261"/>
       <c r="D11" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="271"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
-      <c r="H11" s="255"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="255"/>
-      <c r="K11" s="255"/>
-      <c r="L11" s="255"/>
-      <c r="M11" s="255"/>
-      <c r="N11" s="274"/>
-      <c r="O11" s="284"/>
+      <c r="E11" s="285"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="242"/>
+      <c r="K11" s="242"/>
+      <c r="L11" s="242"/>
+      <c r="M11" s="242"/>
+      <c r="N11" s="257"/>
+      <c r="O11" s="270"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="260" t="s">
+      <c r="A12" s="259" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="261"/>
-      <c r="C12" s="262"/>
+      <c r="B12" s="260"/>
+      <c r="C12" s="261"/>
       <c r="D12" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="272"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="256"/>
-      <c r="H12" s="256"/>
-      <c r="I12" s="256"/>
-      <c r="J12" s="256"/>
-      <c r="K12" s="256"/>
-      <c r="L12" s="256"/>
-      <c r="M12" s="256"/>
-      <c r="N12" s="275"/>
-      <c r="O12" s="281"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
+      <c r="K12" s="243"/>
+      <c r="L12" s="243"/>
+      <c r="M12" s="243"/>
+      <c r="N12" s="258"/>
+      <c r="O12" s="267"/>
     </row>
     <row r="13" spans="1:20" s="25" customFormat="1" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="282"/>
-      <c r="B13" s="283"/>
-      <c r="C13" s="283"/>
-      <c r="D13" s="284"/>
+      <c r="A13" s="268"/>
+      <c r="B13" s="269"/>
+      <c r="C13" s="269"/>
+      <c r="D13" s="270"/>
       <c r="E13" s="20" t="s">
         <v>70</v>
       </c>
@@ -4207,10 +4207,10 @@
       <c r="B14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="291" t="s">
+      <c r="C14" s="250" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="253"/>
+      <c r="D14" s="248"/>
       <c r="E14" s="210">
         <v>0</v>
       </c>
@@ -4253,10 +4253,10 @@
       <c r="B15" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="269" t="s">
+      <c r="C15" s="249" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="253"/>
+      <c r="D15" s="248"/>
       <c r="E15" s="210">
         <f t="shared" ref="E15:N15" si="1">SUM(E16:E18)</f>
         <v>0</v>
@@ -4303,16 +4303,16 @@
       </c>
     </row>
     <row r="16" spans="1:20" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="264" t="s">
+      <c r="A16" s="281" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="292" t="s">
+      <c r="C16" s="252" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="293"/>
+      <c r="D16" s="253"/>
       <c r="E16" s="211">
         <v>0</v>
       </c>
@@ -4349,14 +4349,14 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="265"/>
+      <c r="A17" s="282"/>
       <c r="B17" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="258" t="s">
+      <c r="C17" s="278" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="259"/>
+      <c r="D17" s="279"/>
       <c r="E17" s="211">
         <v>0</v>
       </c>
@@ -4393,14 +4393,14 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="266"/>
+      <c r="A18" s="283"/>
       <c r="B18" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="254" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="268"/>
+      <c r="D18" s="255"/>
       <c r="E18" s="211">
         <v>0</v>
       </c>
@@ -4443,10 +4443,10 @@
       <c r="B19" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="269" t="s">
+      <c r="C19" s="249" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="253"/>
+      <c r="D19" s="248"/>
       <c r="E19" s="210">
         <f t="shared" ref="E19:N19" si="2">SUM(E20:E23)</f>
         <v>0</v>
@@ -4493,16 +4493,16 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="264" t="s">
+      <c r="A20" s="281" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="292" t="s">
+      <c r="C20" s="252" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="293"/>
+      <c r="D20" s="253"/>
       <c r="E20" s="212">
         <v>0</v>
       </c>
@@ -4539,14 +4539,14 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="265"/>
+      <c r="A21" s="282"/>
       <c r="B21" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="263" t="s">
+      <c r="C21" s="280" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="259"/>
+      <c r="D21" s="279"/>
       <c r="E21" s="211">
         <v>0</v>
       </c>
@@ -4583,14 +4583,14 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="265"/>
+      <c r="A22" s="282"/>
       <c r="B22" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="258" t="s">
+      <c r="C22" s="278" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="259"/>
+      <c r="D22" s="279"/>
       <c r="E22" s="211">
         <v>0</v>
       </c>
@@ -4627,14 +4627,14 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="266"/>
+      <c r="A23" s="283"/>
       <c r="B23" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="267" t="s">
+      <c r="C23" s="254" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="268"/>
+      <c r="D23" s="255"/>
       <c r="E23" s="213">
         <v>0</v>
       </c>
@@ -4677,10 +4677,10 @@
       <c r="B24" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="252" t="s">
+      <c r="C24" s="247" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="253"/>
+      <c r="D24" s="248"/>
       <c r="E24" s="29">
         <f t="shared" ref="E24:N24" si="3">(E14+E15)-E19</f>
         <v>0</v>
@@ -4733,10 +4733,10 @@
       <c r="B25" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="247" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="253"/>
+      <c r="D25" s="248"/>
       <c r="E25" s="41">
         <v>0</v>
       </c>
@@ -4918,23 +4918,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="L7:L12"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="N7:N12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A4:O4"/>
-    <mergeCell ref="E6:O6"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="O7:O12"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="I7:I12"/>
@@ -4951,6 +4934,23 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="N7:N12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A4:O4"/>
+    <mergeCell ref="E6:O6"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="O7:O12"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="L7:L12"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C18:D18"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.23622047244094491" bottom="0.23622047244094491" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -5006,98 +5006,98 @@
       <c r="L2" s="68"/>
     </row>
     <row r="3" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="299" t="s">
+      <c r="A3" s="287" t="s">
         <v>46</v>
       </c>
-      <c r="B3" s="300"/>
-      <c r="C3" s="300"/>
-      <c r="D3" s="300"/>
-      <c r="E3" s="300"/>
-      <c r="F3" s="300"/>
-      <c r="G3" s="300"/>
-      <c r="H3" s="300"/>
-      <c r="I3" s="300"/>
-      <c r="J3" s="300"/>
-      <c r="K3" s="300"/>
-      <c r="L3" s="301"/>
+      <c r="B3" s="288"/>
+      <c r="C3" s="288"/>
+      <c r="D3" s="288"/>
+      <c r="E3" s="288"/>
+      <c r="F3" s="288"/>
+      <c r="G3" s="288"/>
+      <c r="H3" s="288"/>
+      <c r="I3" s="288"/>
+      <c r="J3" s="288"/>
+      <c r="K3" s="288"/>
+      <c r="L3" s="289"/>
     </row>
     <row r="4" spans="1:12" s="11" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="306" t="s">
+      <c r="A4" s="294" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="307"/>
-      <c r="C4" s="307"/>
-      <c r="D4" s="307"/>
-      <c r="E4" s="307"/>
-      <c r="F4" s="307"/>
-      <c r="G4" s="307"/>
-      <c r="H4" s="307"/>
-      <c r="I4" s="307"/>
-      <c r="J4" s="307"/>
-      <c r="K4" s="307"/>
-      <c r="L4" s="308"/>
+      <c r="B4" s="295"/>
+      <c r="C4" s="295"/>
+      <c r="D4" s="295"/>
+      <c r="E4" s="295"/>
+      <c r="F4" s="295"/>
+      <c r="G4" s="295"/>
+      <c r="H4" s="295"/>
+      <c r="I4" s="295"/>
+      <c r="J4" s="295"/>
+      <c r="K4" s="295"/>
+      <c r="L4" s="296"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="302"/>
-      <c r="F5" s="303"/>
-      <c r="G5" s="303"/>
-      <c r="H5" s="303"/>
-      <c r="I5" s="303"/>
-      <c r="J5" s="303"/>
-      <c r="K5" s="303"/>
-      <c r="L5" s="304"/>
+      <c r="E5" s="290"/>
+      <c r="F5" s="291"/>
+      <c r="G5" s="291"/>
+      <c r="H5" s="291"/>
+      <c r="I5" s="291"/>
+      <c r="J5" s="291"/>
+      <c r="K5" s="291"/>
+      <c r="L5" s="292"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="276" t="s">
+      <c r="A6" s="262" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="277"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="310" t="s">
+      <c r="B6" s="263"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="264"/>
+      <c r="E6" s="299" t="s">
         <v>116</v>
       </c>
-      <c r="F6" s="289"/>
-      <c r="G6" s="289"/>
-      <c r="H6" s="289"/>
-      <c r="I6" s="289"/>
-      <c r="J6" s="289"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="294" t="s">
+      <c r="F6" s="275"/>
+      <c r="G6" s="275"/>
+      <c r="H6" s="275"/>
+      <c r="I6" s="275"/>
+      <c r="J6" s="275"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="300" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="279"/>
-      <c r="B7" s="280"/>
-      <c r="C7" s="280"/>
-      <c r="D7" s="281"/>
-      <c r="E7" s="270" t="s">
+      <c r="A7" s="265"/>
+      <c r="B7" s="266"/>
+      <c r="C7" s="266"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="284" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="257" t="s">
+      <c r="F7" s="277" t="s">
         <v>119</v>
       </c>
-      <c r="G7" s="254" t="s">
+      <c r="G7" s="251" t="s">
         <v>120</v>
       </c>
-      <c r="H7" s="254" t="s">
+      <c r="H7" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="I7" s="254" t="s">
+      <c r="I7" s="251" t="s">
         <v>122</v>
       </c>
-      <c r="J7" s="296" t="s">
+      <c r="J7" s="301" t="s">
         <v>123</v>
       </c>
-      <c r="K7" s="309" t="s">
+      <c r="K7" s="297" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="295"/>
+      <c r="L7" s="298"/>
     </row>
     <row r="8" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
@@ -5109,14 +5109,14 @@
         <f>'Page 1'!D8</f>
         <v>0</v>
       </c>
-      <c r="E8" s="271"/>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="255"/>
-      <c r="J8" s="297"/>
-      <c r="K8" s="295"/>
-      <c r="L8" s="295"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242"/>
+      <c r="H8" s="242"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="302"/>
+      <c r="K8" s="298"/>
+      <c r="L8" s="298"/>
     </row>
     <row r="9" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -5128,77 +5128,77 @@
         <f>'Page 1'!D9</f>
         <v>BUENAVISTA</v>
       </c>
-      <c r="E9" s="271"/>
-      <c r="F9" s="255"/>
-      <c r="G9" s="255"/>
-      <c r="H9" s="255"/>
-      <c r="I9" s="255"/>
-      <c r="J9" s="297"/>
-      <c r="K9" s="295"/>
-      <c r="L9" s="295"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="242"/>
+      <c r="J9" s="302"/>
+      <c r="K9" s="298"/>
+      <c r="L9" s="298"/>
     </row>
     <row r="10" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="260" t="s">
+      <c r="A10" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="261"/>
-      <c r="C10" s="262"/>
+      <c r="B10" s="260"/>
+      <c r="C10" s="261"/>
       <c r="D10" s="71" t="str">
         <f>'Page 1'!D10</f>
         <v>AGUSAN DEL NORTE</v>
       </c>
-      <c r="E10" s="271"/>
-      <c r="F10" s="255"/>
-      <c r="G10" s="255"/>
-      <c r="H10" s="255"/>
-      <c r="I10" s="255"/>
-      <c r="J10" s="297"/>
-      <c r="K10" s="295"/>
-      <c r="L10" s="295"/>
+      <c r="E10" s="285"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="242"/>
+      <c r="J10" s="302"/>
+      <c r="K10" s="298"/>
+      <c r="L10" s="298"/>
     </row>
     <row r="11" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="260" t="s">
+      <c r="A11" s="259" t="s">
         <v>66</v>
       </c>
-      <c r="B11" s="261"/>
-      <c r="C11" s="262"/>
+      <c r="B11" s="260"/>
+      <c r="C11" s="261"/>
       <c r="D11" s="72" t="str">
         <f>'Page 1'!D11</f>
         <v>10TH JUDICIAL REGION</v>
       </c>
-      <c r="E11" s="271"/>
-      <c r="F11" s="255"/>
-      <c r="G11" s="255"/>
-      <c r="H11" s="255"/>
-      <c r="I11" s="255"/>
-      <c r="J11" s="297"/>
-      <c r="K11" s="295"/>
-      <c r="L11" s="295"/>
+      <c r="E11" s="285"/>
+      <c r="F11" s="242"/>
+      <c r="G11" s="242"/>
+      <c r="H11" s="242"/>
+      <c r="I11" s="242"/>
+      <c r="J11" s="302"/>
+      <c r="K11" s="298"/>
+      <c r="L11" s="298"/>
     </row>
     <row r="12" spans="1:12" s="69" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="260" t="s">
+      <c r="A12" s="259" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="261"/>
-      <c r="C12" s="262"/>
+      <c r="B12" s="260"/>
+      <c r="C12" s="261"/>
       <c r="D12" s="229" t="str">
         <f>'Page 1'!D12</f>
         <v>July 2026</v>
       </c>
-      <c r="E12" s="272"/>
-      <c r="F12" s="256"/>
-      <c r="G12" s="256"/>
-      <c r="H12" s="256"/>
-      <c r="I12" s="256"/>
-      <c r="J12" s="298"/>
-      <c r="K12" s="295"/>
-      <c r="L12" s="295"/>
+      <c r="E12" s="286"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="303"/>
+      <c r="K12" s="298"/>
+      <c r="L12" s="298"/>
     </row>
     <row r="13" spans="1:12" s="69" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="282"/>
-      <c r="B13" s="305"/>
-      <c r="C13" s="305"/>
-      <c r="D13" s="284"/>
+      <c r="A13" s="268"/>
+      <c r="B13" s="293"/>
+      <c r="C13" s="293"/>
+      <c r="D13" s="270"/>
       <c r="E13" s="73" t="s">
         <v>125</v>
       </c>
@@ -5231,10 +5231,10 @@
       <c r="B14" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="291" t="s">
+      <c r="C14" s="250" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="253"/>
+      <c r="D14" s="248"/>
       <c r="E14" s="28">
         <v>4</v>
       </c>
@@ -5269,10 +5269,10 @@
       <c r="B15" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="269" t="s">
+      <c r="C15" s="249" t="s">
         <v>85</v>
       </c>
-      <c r="D15" s="253"/>
+      <c r="D15" s="248"/>
       <c r="E15" s="28">
         <f t="shared" ref="E15:J15" si="1">SUM(E16:E18)</f>
         <v>2</v>
@@ -5307,16 +5307,16 @@
       </c>
     </row>
     <row r="16" spans="1:12" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="264" t="s">
+      <c r="A16" s="281" t="s">
         <v>86</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="292" t="s">
+      <c r="C16" s="252" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="293"/>
+      <c r="D16" s="253"/>
       <c r="E16" s="78">
         <v>2</v>
       </c>
@@ -5345,14 +5345,14 @@
       </c>
     </row>
     <row r="17" spans="1:27" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="265"/>
+      <c r="A17" s="282"/>
       <c r="B17" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="258" t="s">
+      <c r="C17" s="278" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="259"/>
+      <c r="D17" s="279"/>
       <c r="E17" s="33">
         <v>0</v>
       </c>
@@ -5381,14 +5381,14 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="266"/>
+      <c r="A18" s="283"/>
       <c r="B18" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="267" t="s">
+      <c r="C18" s="254" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="268"/>
+      <c r="D18" s="255"/>
       <c r="E18" s="85">
         <v>0</v>
       </c>
@@ -5423,10 +5423,10 @@
       <c r="B19" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="269" t="s">
+      <c r="C19" s="249" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="253"/>
+      <c r="D19" s="248"/>
       <c r="E19" s="28">
         <f t="shared" ref="E19:J19" si="2">SUM(E20:E23)</f>
         <v>5</v>
@@ -5461,16 +5461,16 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="264" t="s">
+      <c r="A20" s="281" t="s">
         <v>95</v>
       </c>
       <c r="B20" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="C20" s="292" t="s">
+      <c r="C20" s="252" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="293"/>
+      <c r="D20" s="253"/>
       <c r="E20" s="78">
         <v>0</v>
       </c>
@@ -5499,14 +5499,14 @@
       </c>
     </row>
     <row r="21" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="265"/>
+      <c r="A21" s="282"/>
       <c r="B21" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="263" t="s">
+      <c r="C21" s="280" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="259"/>
+      <c r="D21" s="279"/>
       <c r="E21" s="33">
         <v>5</v>
       </c>
@@ -5535,14 +5535,14 @@
       </c>
     </row>
     <row r="22" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="265"/>
+      <c r="A22" s="282"/>
       <c r="B22" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="258" t="s">
+      <c r="C22" s="278" t="s">
         <v>101</v>
       </c>
-      <c r="D22" s="259"/>
+      <c r="D22" s="279"/>
       <c r="E22" s="33">
         <v>0</v>
       </c>
@@ -5571,14 +5571,14 @@
       </c>
     </row>
     <row r="23" spans="1:27" s="53" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="266"/>
+      <c r="A23" s="283"/>
       <c r="B23" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="267" t="s">
+      <c r="C23" s="254" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="268"/>
+      <c r="D23" s="255"/>
       <c r="E23" s="85">
         <v>0</v>
       </c>
@@ -5616,10 +5616,10 @@
       <c r="B24" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="C24" s="252" t="s">
+      <c r="C24" s="247" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="253"/>
+      <c r="D24" s="248"/>
       <c r="E24" s="28">
         <f>(E14+E15)-E19</f>
         <v>1</v>
@@ -5660,10 +5660,10 @@
       <c r="B25" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="252" t="s">
+      <c r="C25" s="247" t="s">
         <v>134</v>
       </c>
-      <c r="D25" s="253"/>
+      <c r="D25" s="248"/>
       <c r="E25" s="40">
         <v>0</v>
       </c>
@@ -5842,21 +5842,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="F7:F12"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K7:K12"/>
-    <mergeCell ref="E6:K6"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="G7:G12"/>
     <mergeCell ref="L6:L12"/>
@@ -5873,10 +5858,25 @@
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E7:E12"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K7:K12"/>
+    <mergeCell ref="E6:K6"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="F7:F12"/>
+    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="256" scale="95" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="133" scale="95" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5909,85 +5909,85 @@
       <c r="G2" s="125"/>
     </row>
     <row r="3" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="311" t="s">
+      <c r="A3" s="234" t="s">
         <v>139</v>
       </c>
-      <c r="B3" s="312"/>
-      <c r="C3" s="313"/>
-      <c r="D3" s="313"/>
-      <c r="E3" s="313"/>
-      <c r="F3" s="312"/>
-      <c r="G3" s="312"/>
+      <c r="B3" s="235"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="235"/>
+      <c r="G3" s="235"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="238"/>
-      <c r="B4" s="312"/>
-      <c r="C4" s="313"/>
-      <c r="D4" s="313"/>
-      <c r="E4" s="313"/>
-      <c r="F4" s="312"/>
-      <c r="G4" s="312"/>
+      <c r="A4" s="237"/>
+      <c r="B4" s="235"/>
+      <c r="C4" s="236"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="317" t="s">
+      <c r="A5" s="241" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="319" t="s">
+      <c r="B5" s="245" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="320" t="s">
+      <c r="C5" s="246" t="s">
         <v>142</v>
       </c>
-      <c r="D5" s="318" t="s">
+      <c r="D5" s="244" t="s">
         <v>143</v>
       </c>
-      <c r="E5" s="318" t="s">
+      <c r="E5" s="244" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="319" t="s">
+      <c r="F5" s="245" t="s">
         <v>145</v>
       </c>
-      <c r="G5" s="319" t="s">
+      <c r="G5" s="245" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="255"/>
-      <c r="B6" s="255"/>
-      <c r="C6" s="255"/>
-      <c r="D6" s="255"/>
-      <c r="E6" s="255"/>
-      <c r="F6" s="255"/>
-      <c r="G6" s="255"/>
+      <c r="A6" s="242"/>
+      <c r="B6" s="242"/>
+      <c r="C6" s="242"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="242"/>
+      <c r="F6" s="242"/>
+      <c r="G6" s="242"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="255"/>
-      <c r="B7" s="255"/>
-      <c r="C7" s="255"/>
-      <c r="D7" s="255"/>
-      <c r="E7" s="255"/>
-      <c r="F7" s="255"/>
-      <c r="G7" s="255"/>
+      <c r="A7" s="242"/>
+      <c r="B7" s="242"/>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242"/>
+      <c r="E7" s="242"/>
+      <c r="F7" s="242"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="1:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="256"/>
-      <c r="B8" s="256"/>
-      <c r="C8" s="256"/>
-      <c r="D8" s="256"/>
-      <c r="E8" s="256"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="243"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="314" t="s">
+      <c r="A9" s="238" t="s">
         <v>147</v>
       </c>
-      <c r="B9" s="315"/>
-      <c r="C9" s="315"/>
-      <c r="D9" s="315"/>
-      <c r="E9" s="315"/>
-      <c r="F9" s="315"/>
-      <c r="G9" s="316"/>
+      <c r="B9" s="239"/>
+      <c r="C9" s="239"/>
+      <c r="D9" s="239"/>
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="1:7" s="129" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="132"/>
@@ -6080,15 +6080,15 @@
       <c r="G19" s="135"/>
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="314" t="s">
+      <c r="A20" s="238" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="315"/>
-      <c r="C20" s="315"/>
-      <c r="D20" s="315"/>
-      <c r="E20" s="315"/>
-      <c r="F20" s="315"/>
-      <c r="G20" s="316"/>
+      <c r="B20" s="239"/>
+      <c r="C20" s="239"/>
+      <c r="D20" s="239"/>
+      <c r="E20" s="239"/>
+      <c r="F20" s="239"/>
+      <c r="G20" s="240"/>
     </row>
     <row r="21" spans="1:7" s="129" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="132"/>
@@ -6207,7 +6207,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="256" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="133" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="1048575" man="1"/>
   </colBreaks>
@@ -6240,11 +6240,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="321" t="s">
+      <c r="A1" s="304" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="322"/>
+      <c r="B1" s="305"/>
+      <c r="C1" s="306"/>
       <c r="F1" s="148" t="s">
         <v>151</v>
       </c>
@@ -6512,11 +6512,11 @@
         <v>0</v>
       </c>
       <c r="D20" s="151"/>
-      <c r="F20" s="321" t="s">
+      <c r="F20" s="304" t="s">
         <v>186</v>
       </c>
-      <c r="G20" s="235"/>
-      <c r="H20" s="235"/>
+      <c r="G20" s="305"/>
+      <c r="H20" s="305"/>
       <c r="K20" s="167" t="s">
         <v>187</v>
       </c>
@@ -7103,7 +7103,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.51181102362204722" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="14" scale="90" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="133" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7139,35 +7139,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="234" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="235"/>
-      <c r="M1" s="235"/>
-      <c r="N1" s="235"/>
-      <c r="O1" s="235"/>
-      <c r="P1" s="235"/>
-      <c r="Q1" s="235"/>
-      <c r="R1" s="235"/>
-      <c r="S1" s="235"/>
-      <c r="T1" s="235"/>
-      <c r="U1" s="235"/>
-      <c r="V1" s="235"/>
-      <c r="W1" s="235"/>
-      <c r="X1" s="235"/>
-      <c r="Y1" s="235"/>
-      <c r="Z1" s="235"/>
-      <c r="AA1" s="235"/>
+      <c r="A1" s="314" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="305"/>
+      <c r="C1" s="305"/>
+      <c r="D1" s="305"/>
+      <c r="E1" s="305"/>
+      <c r="F1" s="305"/>
+      <c r="G1" s="305"/>
+      <c r="H1" s="305"/>
+      <c r="I1" s="305"/>
+      <c r="J1" s="305"/>
+      <c r="K1" s="305"/>
+      <c r="L1" s="305"/>
+      <c r="M1" s="305"/>
+      <c r="N1" s="305"/>
+      <c r="O1" s="305"/>
+      <c r="P1" s="305"/>
+      <c r="Q1" s="305"/>
+      <c r="R1" s="305"/>
+      <c r="S1" s="305"/>
+      <c r="T1" s="305"/>
+      <c r="U1" s="305"/>
+      <c r="V1" s="305"/>
+      <c r="W1" s="305"/>
+      <c r="X1" s="305"/>
+      <c r="Y1" s="305"/>
+      <c r="Z1" s="305"/>
+      <c r="AA1" s="305"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="149" t="s">
@@ -7213,7 +7213,7 @@
         <v>5</v>
       </c>
       <c r="Z3" s="182">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7230,13 +7230,13 @@
       <c r="B5" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="307" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="235"/>
-      <c r="E5" s="235"/>
-      <c r="F5" s="235"/>
-      <c r="G5" s="235"/>
+      <c r="D5" s="305"/>
+      <c r="E5" s="305"/>
+      <c r="F5" s="305"/>
+      <c r="G5" s="305"/>
       <c r="H5" s="166"/>
       <c r="I5" s="166"/>
       <c r="J5" s="166"/>
@@ -7255,51 +7255,51 @@
       <c r="Z5" s="184"/>
     </row>
     <row r="6" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="242" t="s">
+      <c r="C6" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="235"/>
-      <c r="E6" s="235"/>
-      <c r="F6" s="235"/>
-      <c r="G6" s="235"/>
+      <c r="D6" s="305"/>
+      <c r="E6" s="305"/>
+      <c r="F6" s="305"/>
+      <c r="G6" s="305"/>
       <c r="H6" s="182">
         <v>0</v>
       </c>
       <c r="N6" s="181"/>
-      <c r="R6" s="251" t="s">
+      <c r="R6" s="312" t="s">
         <v>10</v>
       </c>
-      <c r="S6" s="246"/>
-      <c r="T6" s="246"/>
-      <c r="U6" s="246"/>
-      <c r="V6" s="246"/>
-      <c r="W6" s="246"/>
-      <c r="X6" s="246"/>
-      <c r="Y6" s="246"/>
-      <c r="Z6" s="246"/>
+      <c r="S6" s="313"/>
+      <c r="T6" s="313"/>
+      <c r="U6" s="313"/>
+      <c r="V6" s="313"/>
+      <c r="W6" s="313"/>
+      <c r="X6" s="313"/>
+      <c r="Y6" s="313"/>
+      <c r="Z6" s="313"/>
       <c r="AA6" s="185"/>
     </row>
     <row r="7" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="242" t="s">
+      <c r="C7" s="307" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="235"/>
-      <c r="E7" s="235"/>
-      <c r="F7" s="235"/>
-      <c r="G7" s="235"/>
+      <c r="D7" s="305"/>
+      <c r="E7" s="305"/>
+      <c r="F7" s="305"/>
+      <c r="G7" s="305"/>
       <c r="H7" s="186">
         <v>0</v>
       </c>
       <c r="N7" s="181"/>
-      <c r="R7" s="246"/>
-      <c r="S7" s="246"/>
-      <c r="T7" s="246"/>
-      <c r="U7" s="246"/>
-      <c r="V7" s="246"/>
-      <c r="W7" s="246"/>
-      <c r="X7" s="246"/>
-      <c r="Y7" s="246"/>
-      <c r="Z7" s="246"/>
+      <c r="R7" s="313"/>
+      <c r="S7" s="313"/>
+      <c r="T7" s="313"/>
+      <c r="U7" s="313"/>
+      <c r="V7" s="313"/>
+      <c r="W7" s="313"/>
+      <c r="X7" s="313"/>
+      <c r="Y7" s="313"/>
+      <c r="Z7" s="313"/>
       <c r="AA7" s="185"/>
     </row>
     <row r="8" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7313,15 +7313,15 @@
         <v>0</v>
       </c>
       <c r="N8" s="181"/>
-      <c r="R8" s="246"/>
-      <c r="S8" s="246"/>
-      <c r="T8" s="246"/>
-      <c r="U8" s="246"/>
-      <c r="V8" s="246"/>
-      <c r="W8" s="246"/>
-      <c r="X8" s="246"/>
-      <c r="Y8" s="246"/>
-      <c r="Z8" s="246"/>
+      <c r="R8" s="313"/>
+      <c r="S8" s="313"/>
+      <c r="T8" s="313"/>
+      <c r="U8" s="313"/>
+      <c r="V8" s="313"/>
+      <c r="W8" s="313"/>
+      <c r="X8" s="313"/>
+      <c r="Y8" s="313"/>
+      <c r="Z8" s="313"/>
       <c r="AA8" s="185"/>
     </row>
     <row r="9" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7336,15 +7336,15 @@
         <v>14</v>
       </c>
       <c r="N9" s="181"/>
-      <c r="R9" s="240"/>
-      <c r="S9" s="240"/>
-      <c r="T9" s="240"/>
-      <c r="U9" s="240"/>
-      <c r="V9" s="240"/>
-      <c r="W9" s="240"/>
-      <c r="X9" s="240"/>
-      <c r="Y9" s="240"/>
-      <c r="Z9" s="240"/>
+      <c r="R9" s="311"/>
+      <c r="S9" s="311"/>
+      <c r="T9" s="311"/>
+      <c r="U9" s="311"/>
+      <c r="V9" s="311"/>
+      <c r="W9" s="311"/>
+      <c r="X9" s="311"/>
+      <c r="Y9" s="311"/>
+      <c r="Z9" s="311"/>
       <c r="AA9" s="149"/>
     </row>
     <row r="10" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -7422,13 +7422,13 @@
       <c r="N14" s="181"/>
     </row>
     <row r="15" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="242" t="s">
+      <c r="C15" s="307" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="235"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="235"/>
-      <c r="G15" s="235"/>
+      <c r="D15" s="305"/>
+      <c r="E15" s="305"/>
+      <c r="F15" s="305"/>
+      <c r="G15" s="305"/>
       <c r="H15" s="182">
         <v>0</v>
       </c>
@@ -7442,13 +7442,13 @@
       <c r="AA15" s="149"/>
     </row>
     <row r="16" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="242" t="s">
+      <c r="C16" s="307" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="235"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="235"/>
-      <c r="G16" s="235"/>
+      <c r="D16" s="305"/>
+      <c r="E16" s="305"/>
+      <c r="F16" s="305"/>
+      <c r="G16" s="305"/>
       <c r="H16" s="186">
         <v>0</v>
       </c>
@@ -7534,132 +7534,132 @@
       <c r="N21" s="181"/>
     </row>
     <row r="23" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="247" t="s">
+      <c r="A23" s="321" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="235"/>
-      <c r="C23" s="235"/>
-      <c r="D23" s="235"/>
-      <c r="E23" s="235"/>
-      <c r="F23" s="235"/>
-      <c r="G23" s="235"/>
-      <c r="H23" s="235"/>
-      <c r="I23" s="235"/>
-      <c r="J23" s="235"/>
-      <c r="K23" s="235"/>
-      <c r="L23" s="235"/>
-      <c r="M23" s="235"/>
-      <c r="N23" s="235"/>
-      <c r="O23" s="235"/>
-      <c r="P23" s="235"/>
-      <c r="Q23" s="235"/>
-      <c r="R23" s="235"/>
-      <c r="S23" s="235"/>
-      <c r="T23" s="235"/>
-      <c r="U23" s="235"/>
-      <c r="V23" s="235"/>
-      <c r="W23" s="235"/>
-      <c r="X23" s="235"/>
-      <c r="Y23" s="235"/>
-      <c r="Z23" s="235"/>
-      <c r="AA23" s="235"/>
+      <c r="B23" s="305"/>
+      <c r="C23" s="305"/>
+      <c r="D23" s="305"/>
+      <c r="E23" s="305"/>
+      <c r="F23" s="305"/>
+      <c r="G23" s="305"/>
+      <c r="H23" s="305"/>
+      <c r="I23" s="305"/>
+      <c r="J23" s="305"/>
+      <c r="K23" s="305"/>
+      <c r="L23" s="305"/>
+      <c r="M23" s="305"/>
+      <c r="N23" s="305"/>
+      <c r="O23" s="305"/>
+      <c r="P23" s="305"/>
+      <c r="Q23" s="305"/>
+      <c r="R23" s="305"/>
+      <c r="S23" s="305"/>
+      <c r="T23" s="305"/>
+      <c r="U23" s="305"/>
+      <c r="V23" s="305"/>
+      <c r="W23" s="305"/>
+      <c r="X23" s="305"/>
+      <c r="Y23" s="305"/>
+      <c r="Z23" s="305"/>
+      <c r="AA23" s="305"/>
     </row>
     <row r="26" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="149"/>
       <c r="B26" s="194"/>
       <c r="C26" s="194"/>
-      <c r="D26" s="239" t="s">
+      <c r="D26" s="310" t="s">
         <v>29</v>
       </c>
-      <c r="E26" s="240"/>
-      <c r="F26" s="240"/>
-      <c r="G26" s="240"/>
-      <c r="H26" s="240"/>
-      <c r="I26" s="240"/>
-      <c r="J26" s="240"/>
-      <c r="K26" s="240"/>
-      <c r="L26" s="240"/>
+      <c r="E26" s="311"/>
+      <c r="F26" s="311"/>
+      <c r="G26" s="311"/>
+      <c r="H26" s="311"/>
+      <c r="I26" s="311"/>
+      <c r="J26" s="311"/>
+      <c r="K26" s="311"/>
+      <c r="L26" s="311"/>
       <c r="M26" s="194"/>
       <c r="N26" s="194"/>
       <c r="O26" s="149"/>
       <c r="P26" s="149"/>
       <c r="Q26" s="149"/>
-      <c r="R26" s="239" t="s">
+      <c r="R26" s="310" t="s">
         <v>30</v>
       </c>
-      <c r="S26" s="240"/>
-      <c r="T26" s="240"/>
-      <c r="U26" s="240"/>
-      <c r="V26" s="240"/>
-      <c r="W26" s="240"/>
-      <c r="X26" s="240"/>
-      <c r="Y26" s="240"/>
-      <c r="Z26" s="240"/>
+      <c r="S26" s="311"/>
+      <c r="T26" s="311"/>
+      <c r="U26" s="311"/>
+      <c r="V26" s="311"/>
+      <c r="W26" s="311"/>
+      <c r="X26" s="311"/>
+      <c r="Y26" s="311"/>
+      <c r="Z26" s="311"/>
       <c r="AA26" s="149"/>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C27" s="149"/>
-      <c r="D27" s="248" t="s">
+      <c r="D27" s="308" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="249"/>
-      <c r="F27" s="249"/>
-      <c r="G27" s="249"/>
-      <c r="H27" s="249"/>
-      <c r="I27" s="249"/>
-      <c r="J27" s="249"/>
-      <c r="K27" s="249"/>
-      <c r="L27" s="249"/>
+      <c r="E27" s="309"/>
+      <c r="F27" s="309"/>
+      <c r="G27" s="309"/>
+      <c r="H27" s="309"/>
+      <c r="I27" s="309"/>
+      <c r="J27" s="309"/>
+      <c r="K27" s="309"/>
+      <c r="L27" s="309"/>
       <c r="M27" s="149"/>
       <c r="N27" s="149"/>
       <c r="O27" s="149"/>
       <c r="P27" s="149"/>
       <c r="Q27" s="149"/>
-      <c r="R27" s="248" t="s">
+      <c r="R27" s="308" t="s">
         <v>32</v>
       </c>
-      <c r="S27" s="249"/>
-      <c r="T27" s="249"/>
-      <c r="U27" s="249"/>
-      <c r="V27" s="249"/>
-      <c r="W27" s="249"/>
-      <c r="X27" s="249"/>
-      <c r="Y27" s="249"/>
-      <c r="Z27" s="249"/>
+      <c r="S27" s="309"/>
+      <c r="T27" s="309"/>
+      <c r="U27" s="309"/>
+      <c r="V27" s="309"/>
+      <c r="W27" s="309"/>
+      <c r="X27" s="309"/>
+      <c r="Y27" s="309"/>
+      <c r="Z27" s="309"/>
       <c r="AA27" s="149"/>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D28" s="245"/>
-      <c r="E28" s="246"/>
-      <c r="F28" s="246"/>
-      <c r="G28" s="246"/>
-      <c r="H28" s="246"/>
-      <c r="I28" s="246"/>
-      <c r="J28" s="246"/>
-      <c r="K28" s="246"/>
-      <c r="L28" s="246"/>
-      <c r="R28" s="245"/>
-      <c r="S28" s="246"/>
-      <c r="T28" s="246"/>
-      <c r="U28" s="246"/>
-      <c r="V28" s="246"/>
-      <c r="W28" s="246"/>
-      <c r="X28" s="246"/>
-      <c r="Y28" s="246"/>
-      <c r="Z28" s="246"/>
+      <c r="D28" s="320"/>
+      <c r="E28" s="313"/>
+      <c r="F28" s="313"/>
+      <c r="G28" s="313"/>
+      <c r="H28" s="313"/>
+      <c r="I28" s="313"/>
+      <c r="J28" s="313"/>
+      <c r="K28" s="313"/>
+      <c r="L28" s="313"/>
+      <c r="R28" s="320"/>
+      <c r="S28" s="313"/>
+      <c r="T28" s="313"/>
+      <c r="U28" s="313"/>
+      <c r="V28" s="313"/>
+      <c r="W28" s="313"/>
+      <c r="X28" s="313"/>
+      <c r="Y28" s="313"/>
+      <c r="Z28" s="313"/>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D29" s="238" t="s">
+      <c r="D29" s="237" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="235"/>
-      <c r="F29" s="235"/>
-      <c r="G29" s="235"/>
-      <c r="H29" s="235"/>
-      <c r="I29" s="235"/>
-      <c r="J29" s="235"/>
-      <c r="K29" s="235"/>
-      <c r="L29" s="235"/>
+      <c r="E29" s="305"/>
+      <c r="F29" s="305"/>
+      <c r="G29" s="305"/>
+      <c r="H29" s="305"/>
+      <c r="I29" s="305"/>
+      <c r="J29" s="305"/>
+      <c r="K29" s="305"/>
+      <c r="L29" s="305"/>
       <c r="P29" s="166"/>
       <c r="Q29" s="166"/>
       <c r="R29" s="166"/>
@@ -7769,37 +7769,37 @@
       <c r="AA33" s="166"/>
     </row>
     <row r="34" spans="1:27" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="238" t="s">
+      <c r="A34" s="237" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="235"/>
-      <c r="C34" s="235"/>
-      <c r="D34" s="235"/>
-      <c r="E34" s="235"/>
-      <c r="F34" s="235"/>
+      <c r="B34" s="305"/>
+      <c r="C34" s="305"/>
+      <c r="D34" s="305"/>
+      <c r="E34" s="305"/>
+      <c r="F34" s="305"/>
       <c r="G34" s="197"/>
       <c r="H34" s="166" t="s">
         <v>38</v>
       </c>
-      <c r="I34" s="241" t="str">
+      <c r="I34" s="317" t="str">
         <f ca="1">TEXT(TODAY(), "mmmm yyyy")</f>
         <v>August 2026</v>
       </c>
-      <c r="J34" s="240"/>
-      <c r="K34" s="240"/>
-      <c r="L34" s="240"/>
-      <c r="M34" s="240"/>
-      <c r="N34" s="240"/>
+      <c r="J34" s="311"/>
+      <c r="K34" s="311"/>
+      <c r="L34" s="311"/>
+      <c r="M34" s="311"/>
+      <c r="N34" s="311"/>
       <c r="O34" s="166" t="s">
         <v>39</v>
       </c>
-      <c r="P34" s="243" t="s">
+      <c r="P34" s="318" t="s">
         <v>40</v>
       </c>
-      <c r="Q34" s="244"/>
-      <c r="R34" s="244"/>
-      <c r="S34" s="244"/>
-      <c r="T34" s="244"/>
+      <c r="Q34" s="319"/>
+      <c r="R34" s="319"/>
+      <c r="S34" s="319"/>
+      <c r="T34" s="319"/>
       <c r="U34" s="184"/>
       <c r="V34" s="195"/>
       <c r="W34" s="195"/>
@@ -7817,16 +7817,16 @@
       <c r="AA36" s="198"/>
     </row>
     <row r="37" spans="1:27" ht="29.1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J37" s="250"/>
-      <c r="K37" s="240"/>
-      <c r="L37" s="240"/>
-      <c r="M37" s="240"/>
-      <c r="N37" s="240"/>
-      <c r="O37" s="240"/>
-      <c r="P37" s="240"/>
-      <c r="Q37" s="240"/>
-      <c r="R37" s="240"/>
-      <c r="S37" s="240"/>
+      <c r="J37" s="322"/>
+      <c r="K37" s="311"/>
+      <c r="L37" s="311"/>
+      <c r="M37" s="311"/>
+      <c r="N37" s="311"/>
+      <c r="O37" s="311"/>
+      <c r="P37" s="311"/>
+      <c r="Q37" s="311"/>
+      <c r="R37" s="311"/>
+      <c r="S37" s="311"/>
       <c r="T37" s="149"/>
       <c r="U37" s="149"/>
       <c r="V37" s="149"/>
@@ -7837,18 +7837,18 @@
       <c r="AA37" s="149"/>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="J38" s="248" t="s">
+      <c r="J38" s="308" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="249"/>
-      <c r="L38" s="249"/>
-      <c r="M38" s="249"/>
-      <c r="N38" s="249"/>
-      <c r="O38" s="249"/>
-      <c r="P38" s="249"/>
-      <c r="Q38" s="249"/>
-      <c r="R38" s="249"/>
-      <c r="S38" s="249"/>
+      <c r="K38" s="309"/>
+      <c r="L38" s="309"/>
+      <c r="M38" s="309"/>
+      <c r="N38" s="309"/>
+      <c r="O38" s="309"/>
+      <c r="P38" s="309"/>
+      <c r="Q38" s="309"/>
+      <c r="R38" s="309"/>
+      <c r="S38" s="309"/>
       <c r="T38" s="149"/>
       <c r="U38" s="149"/>
       <c r="V38" s="149"/>
@@ -7859,37 +7859,37 @@
       <c r="AA38" s="149"/>
     </row>
     <row r="40" spans="1:27" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="237" t="s">
+      <c r="A40" s="316" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="235"/>
-      <c r="C40" s="235"/>
-      <c r="D40" s="236" t="s">
+      <c r="B40" s="305"/>
+      <c r="C40" s="305"/>
+      <c r="D40" s="315" t="s">
         <v>43</v>
       </c>
-      <c r="E40" s="235"/>
-      <c r="F40" s="235"/>
-      <c r="G40" s="235"/>
-      <c r="H40" s="235"/>
-      <c r="I40" s="235"/>
-      <c r="J40" s="235"/>
-      <c r="K40" s="235"/>
-      <c r="L40" s="235"/>
-      <c r="M40" s="235"/>
-      <c r="N40" s="235"/>
-      <c r="O40" s="235"/>
-      <c r="P40" s="235"/>
-      <c r="Q40" s="235"/>
-      <c r="R40" s="235"/>
-      <c r="S40" s="235"/>
-      <c r="T40" s="235"/>
-      <c r="U40" s="235"/>
-      <c r="V40" s="235"/>
-      <c r="W40" s="235"/>
-      <c r="X40" s="235"/>
-      <c r="Y40" s="235"/>
-      <c r="Z40" s="235"/>
-      <c r="AA40" s="235"/>
+      <c r="E40" s="305"/>
+      <c r="F40" s="305"/>
+      <c r="G40" s="305"/>
+      <c r="H40" s="305"/>
+      <c r="I40" s="305"/>
+      <c r="J40" s="305"/>
+      <c r="K40" s="305"/>
+      <c r="L40" s="305"/>
+      <c r="M40" s="305"/>
+      <c r="N40" s="305"/>
+      <c r="O40" s="305"/>
+      <c r="P40" s="305"/>
+      <c r="Q40" s="305"/>
+      <c r="R40" s="305"/>
+      <c r="S40" s="305"/>
+      <c r="T40" s="305"/>
+      <c r="U40" s="305"/>
+      <c r="V40" s="305"/>
+      <c r="W40" s="305"/>
+      <c r="X40" s="305"/>
+      <c r="Y40" s="305"/>
+      <c r="Z40" s="305"/>
+      <c r="AA40" s="305"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="C41" s="146"/>
@@ -7927,12 +7927,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="R27:Z27"/>
-    <mergeCell ref="R26:Z26"/>
-    <mergeCell ref="R6:Z9"/>
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="D40:AA40"/>
     <mergeCell ref="A40:C40"/>
@@ -7949,10 +7943,16 @@
     <mergeCell ref="D29:L29"/>
     <mergeCell ref="R28:Z28"/>
     <mergeCell ref="D27:L27"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="R27:Z27"/>
+    <mergeCell ref="R26:Z26"/>
+    <mergeCell ref="R6:Z9"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="256" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="133" scale="90" firstPageNumber="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7981,7 +7981,7 @@
       <c r="H30" s="324"/>
       <c r="I30" s="324"/>
       <c r="J30" s="324"/>
-      <c r="K30" s="284"/>
+      <c r="K30" s="270"/>
     </row>
     <row r="31" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D31" s="202"/>
@@ -7997,7 +7997,7 @@
       <c r="H32" s="324"/>
       <c r="I32" s="324"/>
       <c r="J32" s="324"/>
-      <c r="K32" s="284"/>
+      <c r="K32" s="270"/>
     </row>
     <row r="33" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D33" s="202"/>
@@ -8013,7 +8013,7 @@
       <c r="H34" s="324"/>
       <c r="I34" s="324"/>
       <c r="J34" s="324"/>
-      <c r="K34" s="284"/>
+      <c r="K34" s="270"/>
     </row>
     <row r="35" spans="4:11" x14ac:dyDescent="0.2">
       <c r="D35" s="202"/>
